--- a/alunos/Christian_Wis/semana_04/base_rh.xlsx
+++ b/alunos/Christian_Wis/semana_04/base_rh.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -750,17 +750,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Joï¿½o Miguel da Costa</t>
+          <t>João Miguel da Costa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Laï¿½s da Mata</t>
+          <t>Laís da Mata</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Joï¿½o Felipe da Cunha</t>
+          <t>João Felipe da Cunha</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Maria Cecï¿½lia Teixeira</t>
+          <t>Maria Cecília Teixeira</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Sr. Henrique Fogaï¿½a</t>
+          <t>Sr. Henrique Fogaça</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cecï¿½lia Silveira</t>
+          <t>Cecília Silveira</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Srta. Ana Lï¿½via Alves</t>
+          <t>Srta. Ana Lívia Alves</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dra. Letï¿½cia Jesus</t>
+          <t>Dra. Letícia Jesus</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Maitï¿½ da Mota</t>
+          <t>Maitê da Mota</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Joï¿½o Miguel Teixeira</t>
+          <t>João Miguel Teixeira</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cauï¿½ Monteiro</t>
+          <t>Cauã Monteiro</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Maria Julia Araï¿½jo</t>
+          <t>Maria Julia Araújo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dr. Andrï¿½ Ramos</t>
+          <t>Dr. André Ramos</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Joï¿½o Gabriel Caldeira</t>
+          <t>João Gabriel Caldeira</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -3740,17 +3740,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Benï¿½cio Monteiro</t>
+          <t>Benício Monteiro</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Joï¿½o Barbosa</t>
+          <t>João Barbosa</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Jï¿½lia Araï¿½jo</t>
+          <t>Júlia Araújo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Isabel Fogaï¿½a</t>
+          <t>Isabel Fogaça</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Lucca Araï¿½jo</t>
+          <t>Lucca Araújo</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cauï¿½ Silva</t>
+          <t>Cauã Silva</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Jï¿½lia Cardoso</t>
+          <t>Júlia Cardoso</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ana Fogaï¿½a</t>
+          <t>Ana Fogaça</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Helena Gonï¿½alves</t>
+          <t>Helena Gonçalves</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Luiz Otï¿½vio Novaes</t>
+          <t>Luiz Otávio Novaes</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5120,17 +5120,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Brenda Aragï¿½o</t>
+          <t>Brenda Aragão</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ana Jï¿½lia da Luz</t>
+          <t>Ana Júlia da Luz</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Joï¿½o Pedro Rodrigues</t>
+          <t>João Pedro Rodrigues</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Eloah Araï¿½jo</t>
+          <t>Eloah Araújo</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -6086,12 +6086,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sr. Joï¿½o Lucas da Mota</t>
+          <t>Sr. João Lucas da Mota</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Joï¿½o Gabriel Lopes</t>
+          <t>João Gabriel Lopes</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Lï¿½via Barros</t>
+          <t>Lívia Barros</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6418,7 +6418,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -6546,12 +6546,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Cauï¿½ Fernandes</t>
+          <t>Cauã Fernandes</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E135" t="n">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Sr. Antï¿½nio Silveira</t>
+          <t>Sr. Antônio Silveira</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E147" t="n">
@@ -7190,17 +7190,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Laï¿½s Melo</t>
+          <t>Laís Melo</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Alï¿½cia Ribeiro</t>
+          <t>Alícia Ribeiro</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E150" t="n">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E152" t="n">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E153" t="n">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Joï¿½o Silva</t>
+          <t>João Silva</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E159" t="n">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Sr. Benï¿½cio Ribeiro</t>
+          <t>Sr. Benício Ribeiro</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E165" t="n">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8294,17 +8294,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Cauï¿½ Cardoso</t>
+          <t>Cauã Cardoso</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E172" t="n">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Lavï¿½nia Martins</t>
+          <t>Lavínia Martins</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -8851,12 +8851,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E184" t="n">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9076,7 +9076,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Ana Jï¿½lia Cardoso</t>
+          <t>Ana Júlia Cardoso</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -9122,17 +9122,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Joï¿½o Pereira</t>
+          <t>João Pereira</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Laï¿½s Rodrigues</t>
+          <t>Laís Rodrigues</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -9357,12 +9357,12 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Maitï¿½ Gomes</t>
+          <t>Maitê Gomes</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Alice Gonï¿½alves</t>
+          <t>Alice Gonçalves</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Sra. Bï¿½rbara Correia</t>
+          <t>Sra. Bárbara Correia</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -9858,12 +9858,12 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Thales Fogaï¿½a</t>
+          <t>Thales Fogaça</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10144,7 +10144,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Laï¿½s Aragï¿½o</t>
+          <t>Laís Aragão</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Cauï¿½ Ramos</t>
+          <t>Cauã Ramos</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -10512,7 +10512,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Maitï¿½ da Luz</t>
+          <t>Maitê da Luz</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -10732,12 +10732,12 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Jï¿½lia Duarte</t>
+          <t>Júlia Duarte</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Maria Cecï¿½lia Farias</t>
+          <t>Maria Cecília Farias</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Ana Jï¿½lia Melo</t>
+          <t>Ana Júlia Melo</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -11197,12 +11197,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -11294,7 +11294,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E237" t="n">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E242" t="n">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Joï¿½o Miguel Ribeiro</t>
+          <t>João Miguel Ribeiro</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -11754,7 +11754,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E254" t="n">
@@ -12117,12 +12117,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E255" t="n">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -12214,7 +12214,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E257" t="n">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Joï¿½o Miguel Santos</t>
+          <t>João Miguel Santos</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12480,12 +12480,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Isabelly da Conceiï¿½ï¿½o</t>
+          <t>Isabelly da Conceição</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12526,12 +12526,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Dra. Maitï¿½ Gonï¿½alves</t>
+          <t>Dra. Maitê Gonçalves</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12715,7 +12715,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -12802,7 +12802,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Ana Vitï¿½ria Pires</t>
+          <t>Ana Vitória Pires</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -12812,7 +12812,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -12853,7 +12853,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Joï¿½o Lucas Monteiro</t>
+          <t>João Lucas Monteiro</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -12945,12 +12945,12 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E273" t="n">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -13078,7 +13078,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Joï¿½o Vitor da Conceiï¿½ï¿½o</t>
+          <t>João Vitor da Conceição</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Joï¿½o Miguel Aragï¿½o</t>
+          <t>João Miguel Aragão</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E279" t="n">
@@ -13247,7 +13247,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13497,7 +13497,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E286" t="n">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -13937,7 +13937,7 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -14167,7 +14167,7 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Maria Cecï¿½lia Almeida</t>
+          <t>Maria Cecília Almeida</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -14279,7 +14279,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14489,7 +14489,7 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
@@ -14509,7 +14509,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14765,7 +14765,7 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
@@ -14831,7 +14831,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
@@ -15056,17 +15056,17 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Alï¿½cia Cavalcanti</t>
+          <t>Alícia Cavalcanti</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E319" t="n">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15179,7 +15179,7 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Antï¿½nio Oliveira</t>
+          <t>Antônio Oliveira</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -15424,7 +15424,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Lï¿½via Pires</t>
+          <t>Lívia Pires</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -15547,7 +15547,7 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
@@ -15567,7 +15567,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
@@ -15654,7 +15654,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Luiz Henrique Aragï¿½o</t>
+          <t>Luiz Henrique Aragão</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -15751,7 +15751,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
@@ -15848,7 +15848,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E336" t="n">
@@ -16027,7 +16027,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -16073,7 +16073,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -16298,12 +16298,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Natï¿½lia Costela</t>
+          <t>Natália Costela</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Otï¿½vio Duarte</t>
+          <t>Otávio Duarte</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -16400,7 +16400,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E348" t="n">
@@ -16436,7 +16436,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Clara da Conceiï¿½ï¿½o</t>
+          <t>Clara da Conceição</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -16487,12 +16487,12 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E350" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -16620,12 +16620,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Lï¿½via Farias</t>
+          <t>Lívia Farias</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -16671,12 +16671,12 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E354" t="n">
@@ -16697,7 +16697,7 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
@@ -16789,7 +16789,7 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
@@ -16850,7 +16850,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Lavï¿½nia da Costa</t>
+          <t>Lavínia da Costa</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -16896,7 +16896,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Joï¿½o Pedro Souza</t>
+          <t>João Pedro Souza</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
@@ -17065,7 +17065,7 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
@@ -17111,7 +17111,7 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
@@ -17264,7 +17264,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Dr. Joï¿½o Vitor Correia</t>
+          <t>Dr. João Vitor Correia</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -17274,7 +17274,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E367" t="n">
@@ -17361,7 +17361,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -17387,7 +17387,7 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
@@ -17402,7 +17402,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Maria Alice Fogaï¿½a</t>
+          <t>Maria Alice Fogaça</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -17632,12 +17632,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Joï¿½o Pedro Costa</t>
+          <t>João Pedro Costa</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -17688,7 +17688,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E376" t="n">
@@ -17709,7 +17709,7 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
@@ -17770,7 +17770,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Sra. Yasmin Araï¿½jo</t>
+          <t>Sra. Yasmin Araújo</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Sofia Gonï¿½alves</t>
+          <t>Sofia Gonçalves</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -17847,7 +17847,7 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
@@ -17872,7 +17872,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E380" t="n">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
@@ -17913,7 +17913,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Lavï¿½nia Martins</t>
+          <t>Lavínia Martins</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -18092,7 +18092,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Heloï¿½sa Dias</t>
+          <t>Heloísa Dias</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -18102,7 +18102,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E385" t="n">
@@ -18123,7 +18123,7 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
@@ -18184,12 +18184,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Gustavo Henrique Fogaï¿½a</t>
+          <t>Gustavo Henrique Fogaça</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -18215,7 +18215,7 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -18353,7 +18353,7 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
@@ -18373,7 +18373,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -18399,7 +18399,7 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
@@ -18511,7 +18511,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -18583,7 +18583,7 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
@@ -18700,7 +18700,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E398" t="n">
@@ -18782,7 +18782,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Maria Vitï¿½ria Costa</t>
+          <t>Maria Vitória Costa</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -19043,7 +19043,7 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
@@ -19063,7 +19063,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -19114,7 +19114,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E407" t="n">
@@ -19181,7 +19181,7 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Miguel Araï¿½jo</t>
+          <t>Miguel Araújo</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -19344,7 +19344,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E412" t="n">
@@ -19380,7 +19380,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Joï¿½o Lucas da Cunha</t>
+          <t>João Lucas da Cunha</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -19477,7 +19477,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -19595,7 +19595,7 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
@@ -19656,7 +19656,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Ana Vitï¿½ria Monteiro</t>
+          <t>Ana Vitória Monteiro</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -19917,7 +19917,7 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
@@ -19978,12 +19978,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Murilo Araï¿½jo</t>
+          <t>Murilo Araújo</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -20101,7 +20101,7 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
@@ -20208,12 +20208,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Vicente Aragï¿½o</t>
+          <t>Vicente Aragão</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
@@ -20264,7 +20264,7 @@
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E432" t="n">
@@ -20305,7 +20305,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
@@ -20392,7 +20392,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Sra. Manuela Fogaï¿½a</t>
+          <t>Sra. Manuela Fogaça</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
@@ -20448,7 +20448,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E436" t="n">
@@ -20469,7 +20469,7 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
@@ -20632,7 +20632,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E440" t="n">
@@ -20653,7 +20653,7 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -20760,12 +20760,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Ana Jï¿½lia Moraes</t>
+          <t>Ana Júlia Moraes</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E444" t="n">
@@ -20857,7 +20857,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -20903,7 +20903,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -20944,12 +20944,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Marina Aragï¿½o</t>
+          <t>Marina Aragão</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -21041,12 +21041,12 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E449" t="n">
@@ -21087,7 +21087,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -21133,7 +21133,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
@@ -21220,7 +21220,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Laï¿½s Gomes</t>
+          <t>Laís Gomes</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -21230,7 +21230,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E453" t="n">
@@ -21251,7 +21251,7 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
@@ -21266,7 +21266,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Joï¿½o Miguel Azevedo</t>
+          <t>João Miguel Azevedo</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -21297,7 +21297,7 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -21343,7 +21343,7 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
@@ -21363,7 +21363,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -21409,7 +21409,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -21588,12 +21588,12 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Vitï¿½ria Caldeira</t>
+          <t>Vitória Caldeira</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Davi Gonï¿½alves</t>
+          <t>Davi Gonçalves</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -21665,7 +21665,7 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E464" t="n">
@@ -21864,7 +21864,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Maria Vitï¿½ria Costela</t>
+          <t>Maria Vitória Costela</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -21915,12 +21915,12 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E468" t="n">
@@ -21961,7 +21961,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -22033,7 +22033,7 @@
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
@@ -22048,12 +22048,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Sr. Joï¿½o Vitor Pinto</t>
+          <t>Sr. João Vitor Pinto</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -22079,7 +22079,7 @@
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
@@ -22099,7 +22099,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -22145,12 +22145,12 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E473" t="n">
@@ -22196,7 +22196,7 @@
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E474" t="n">
@@ -22278,12 +22278,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Sr. Davi Luiz Aragï¿½o</t>
+          <t>Sr. Davi Luiz Aragão</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -22324,7 +22324,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Letï¿½cia Caldeira</t>
+          <t>Letícia Caldeira</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -22380,7 +22380,7 @@
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E478" t="n">
@@ -22447,7 +22447,7 @@
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
@@ -22467,7 +22467,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -22513,7 +22513,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -22539,7 +22539,7 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
@@ -22559,7 +22559,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -22600,12 +22600,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Brenda Fogaï¿½a</t>
+          <t>Brenda Fogaça</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
@@ -22646,17 +22646,17 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Sra. Alana Fogaï¿½a</t>
+          <t>Sra. Alana Fogaça</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E484" t="n">
@@ -22677,7 +22677,7 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
@@ -22723,7 +22723,7 @@
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
@@ -22769,7 +22769,7 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
@@ -22789,12 +22789,12 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E487" t="n">
@@ -22881,7 +22881,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -22927,7 +22927,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -22968,7 +22968,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Luiz Otï¿½vio Nogueira</t>
+          <t>Luiz Otávio Nogueira</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -22978,7 +22978,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E491" t="n">
@@ -22999,7 +22999,7 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Ana Jï¿½lia Novaes</t>
+          <t>Ana Júlia Novaes</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -23045,7 +23045,7 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
@@ -23065,7 +23065,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -23203,7 +23203,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -23275,7 +23275,7 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
@@ -23336,7 +23336,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Joï¿½o Gabriel Azevedo</t>
+          <t>João Gabriel Azevedo</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -23367,7 +23367,7 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
@@ -23392,7 +23392,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E500" t="n">
@@ -23459,7 +23459,7 @@
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
@@ -23474,7 +23474,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Joï¿½o Silveira</t>
+          <t>João Silveira</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Dr. Joï¿½o Felipe Novaes</t>
+          <t>Dr. João Felipe Novaes</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -23617,7 +23617,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -23643,7 +23643,7 @@
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
@@ -23663,7 +23663,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -23750,12 +23750,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Luiz Felipe Aragï¿½o</t>
+          <t>Luiz Felipe Aragão</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -23893,7 +23893,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -23919,7 +23919,7 @@
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J511" t="inlineStr">
@@ -24026,7 +24026,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Pedro Gonï¿½alves</t>
+          <t>Pedro Gonçalves</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J514" t="inlineStr">
@@ -24128,7 +24128,7 @@
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E516" t="n">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J516" t="inlineStr">
@@ -24164,12 +24164,12 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Sra. Natï¿½lia Gomes</t>
+          <t>Sra. Natália Gomes</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -24261,12 +24261,12 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E519" t="n">
@@ -24358,7 +24358,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E521" t="n">
@@ -24440,12 +24440,12 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Vitï¿½ria Porto</t>
+          <t>Vitória Porto</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -24655,7 +24655,7 @@
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
@@ -24675,7 +24675,7 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -24701,7 +24701,7 @@
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
@@ -24767,7 +24767,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -24839,7 +24839,7 @@
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
@@ -24905,7 +24905,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -24931,7 +24931,7 @@
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
@@ -24951,7 +24951,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -25038,12 +25038,12 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Andrï¿½ Ramos</t>
+          <t>André Ramos</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -25089,12 +25089,12 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E537" t="n">
@@ -25115,7 +25115,7 @@
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J537" t="inlineStr">
@@ -25161,7 +25161,7 @@
       </c>
       <c r="I538" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J538" t="inlineStr">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -25222,7 +25222,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Sr. Joï¿½o Vitor Melo</t>
+          <t>Sr. João Vitor Melo</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -25253,7 +25253,7 @@
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
@@ -25314,12 +25314,12 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Marcos Vinicius Fogaï¿½a</t>
+          <t>Marcos Vinicius Fogaça</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -25345,7 +25345,7 @@
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J542" t="inlineStr">
@@ -25365,7 +25365,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -25406,7 +25406,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Luiz Miguel Fogaï¿½a</t>
+          <t>Luiz Miguel Fogaça</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -25457,7 +25457,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -25503,7 +25503,7 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -25728,7 +25728,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Maria Vitï¿½ria Fogaï¿½a</t>
+          <t>Maria Vitória Fogaça</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="I551" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J551" t="inlineStr">
@@ -25825,7 +25825,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -25866,7 +25866,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Alexia Araï¿½jo</t>
+          <t>Alexia Araújo</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -25897,7 +25897,7 @@
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J554" t="inlineStr">
@@ -25912,7 +25912,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Lï¿½via da Paz</t>
+          <t>Lívia da Paz</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -25968,7 +25968,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E556" t="n">
@@ -26050,7 +26050,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Dra. Ana Laura Fogaï¿½a</t>
+          <t>Dra. Ana Laura Fogaça</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -26147,7 +26147,7 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -26193,7 +26193,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -26244,7 +26244,7 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E562" t="n">
@@ -26280,7 +26280,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Dr. Joï¿½o da Mata</t>
+          <t>Dr. João da Mata</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
@@ -26290,7 +26290,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E563" t="n">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E564" t="n">
@@ -26469,12 +26469,12 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E567" t="n">
@@ -26495,7 +26495,7 @@
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J567" t="inlineStr">
@@ -26515,7 +26515,7 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -26633,7 +26633,7 @@
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J570" t="inlineStr">
@@ -26745,7 +26745,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -26878,7 +26878,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Letï¿½cia Silva</t>
+          <t>Letícia Silva</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -26888,7 +26888,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E576" t="n">
@@ -26924,7 +26924,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Ana Vitï¿½ria Melo</t>
+          <t>Ana Vitória Melo</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
@@ -27001,7 +27001,7 @@
       </c>
       <c r="I578" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J578" t="inlineStr">
@@ -27139,7 +27139,7 @@
       </c>
       <c r="I581" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J581" t="inlineStr">
@@ -27251,7 +27251,7 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -27338,17 +27338,17 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Dra. Alï¿½cia Nascimento</t>
+          <t>Dra. Alícia Nascimento</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E586" t="n">
@@ -27435,7 +27435,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
@@ -27461,7 +27461,7 @@
       </c>
       <c r="I588" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J588" t="inlineStr">
@@ -27486,7 +27486,7 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E589" t="n">
@@ -27507,7 +27507,7 @@
       </c>
       <c r="I589" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J589" t="inlineStr">
@@ -27527,7 +27527,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -27599,7 +27599,7 @@
       </c>
       <c r="I591" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J591" t="inlineStr">
@@ -27614,12 +27614,12 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Srta. Lavï¿½nia Campos</t>
+          <t>Srta. Lavínia Campos</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -27645,7 +27645,7 @@
       </c>
       <c r="I592" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J592" t="inlineStr">
@@ -27660,7 +27660,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Breno Gonï¿½alves</t>
+          <t>Breno Gonçalves</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -27691,7 +27691,7 @@
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J593" t="inlineStr">
@@ -27762,7 +27762,7 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E595" t="n">
@@ -27803,7 +27803,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -27849,7 +27849,7 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -27890,12 +27890,12 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Joï¿½o Pedro Pereira</t>
+          <t>João Pedro Pereira</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -27921,7 +27921,7 @@
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
@@ -28079,7 +28079,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -28105,7 +28105,7 @@
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
@@ -28120,7 +28120,7 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Dr. Antï¿½nio Azevedo</t>
+          <t>Dr. Antônio Azevedo</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
@@ -28197,7 +28197,7 @@
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
@@ -28289,7 +28289,7 @@
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J606" t="inlineStr">
@@ -28309,7 +28309,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -28335,7 +28335,7 @@
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J607" t="inlineStr">
@@ -28355,7 +28355,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -28442,12 +28442,12 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Renan Araï¿½jo</t>
+          <t>Renan Araújo</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -28565,7 +28565,7 @@
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J612" t="inlineStr">
@@ -28585,12 +28585,12 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E613" t="n">
@@ -28611,7 +28611,7 @@
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J613" t="inlineStr">
@@ -28626,7 +28626,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Joï¿½o Peixoto</t>
+          <t>João Peixoto</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -28703,7 +28703,7 @@
       </c>
       <c r="I615" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J615" t="inlineStr">
@@ -28841,7 +28841,7 @@
       </c>
       <c r="I618" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J618" t="inlineStr">
@@ -28887,7 +28887,7 @@
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J619" t="inlineStr">
@@ -28902,12 +28902,12 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Heloï¿½sa Alves</t>
+          <t>Heloísa Alves</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -28979,7 +28979,7 @@
       </c>
       <c r="I621" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J621" t="inlineStr">
@@ -29025,7 +29025,7 @@
       </c>
       <c r="I622" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J622" t="inlineStr">
@@ -29050,7 +29050,7 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E623" t="n">
@@ -29071,7 +29071,7 @@
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J623" t="inlineStr">
@@ -29091,7 +29091,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
@@ -29178,7 +29178,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Elisa Aragï¿½o</t>
+          <t>Elisa Aragão</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -29188,7 +29188,7 @@
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E626" t="n">
@@ -29229,12 +29229,12 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E627" t="n">
@@ -29326,7 +29326,7 @@
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E629" t="n">
@@ -29347,7 +29347,7 @@
       </c>
       <c r="I629" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J629" t="inlineStr">
@@ -29367,7 +29367,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -29393,7 +29393,7 @@
       </c>
       <c r="I630" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J630" t="inlineStr">
@@ -29418,7 +29418,7 @@
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E631" t="n">
@@ -29505,7 +29505,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -29597,7 +29597,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -29623,7 +29623,7 @@
       </c>
       <c r="I635" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J635" t="inlineStr">
@@ -29669,7 +29669,7 @@
       </c>
       <c r="I636" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J636" t="inlineStr">
@@ -29735,7 +29735,7 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Benï¿½cio Moreira</t>
+          <t>Benício Moreira</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -29827,7 +29827,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -29899,7 +29899,7 @@
       </c>
       <c r="I641" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J641" t="inlineStr">
@@ -29924,7 +29924,7 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E642" t="n">
@@ -30052,7 +30052,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Benï¿½cio Castro</t>
+          <t>Benício Castro</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -30098,17 +30098,17 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Marcos Vinicius Aragï¿½o</t>
+          <t>Marcos Vinicius Aragão</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E646" t="n">
@@ -30241,7 +30241,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -30267,7 +30267,7 @@
       </c>
       <c r="I649" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J649" t="inlineStr">
@@ -30282,7 +30282,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Vitï¿½ria Jesus</t>
+          <t>Vitória Jesus</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -30313,7 +30313,7 @@
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J650" t="inlineStr">
@@ -30328,7 +30328,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Maria Araï¿½jo</t>
+          <t>Maria Araújo</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -30374,7 +30374,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Alï¿½cia Porto</t>
+          <t>Alícia Porto</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -30471,7 +30471,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -30563,7 +30563,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -30589,7 +30589,7 @@
       </c>
       <c r="I656" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J656" t="inlineStr">
@@ -30655,12 +30655,12 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E658" t="n">
@@ -30747,12 +30747,12 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E660" t="n">
@@ -30788,7 +30788,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Bï¿½rbara da Cunha</t>
+          <t>Bárbara da Cunha</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
@@ -30931,7 +30931,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -30972,7 +30972,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Benï¿½cio Rodrigues</t>
+          <t>Benício Rodrigues</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -31028,7 +31028,7 @@
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E666" t="n">
@@ -31110,12 +31110,12 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Cecï¿½lia da Rosa</t>
+          <t>Cecília da Rosa</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -31141,7 +31141,7 @@
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
@@ -31166,7 +31166,7 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E669" t="n">
@@ -31207,7 +31207,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -31233,7 +31233,7 @@
       </c>
       <c r="I670" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J670" t="inlineStr">
@@ -31345,7 +31345,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -31386,7 +31386,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Ana Jï¿½lia Cunha</t>
+          <t>Ana Júlia Cunha</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -31437,7 +31437,7 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -31483,7 +31483,7 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -31534,7 +31534,7 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E677" t="n">
@@ -31555,7 +31555,7 @@
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
@@ -31601,7 +31601,7 @@
       </c>
       <c r="I678" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J678" t="inlineStr">
@@ -31739,7 +31739,7 @@
       </c>
       <c r="I681" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J681" t="inlineStr">
@@ -31759,7 +31759,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
@@ -31831,7 +31831,7 @@
       </c>
       <c r="I683" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J683" t="inlineStr">
@@ -31846,7 +31846,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>Natï¿½lia Azevedo</t>
+          <t>Natália Azevedo</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -31877,7 +31877,7 @@
       </c>
       <c r="I684" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J684" t="inlineStr">
@@ -31897,7 +31897,7 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -31943,12 +31943,12 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E686" t="n">
@@ -31984,7 +31984,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Sra. Maria Vitï¿½ria Pires</t>
+          <t>Sra. Maria Vitória Pires</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -31994,7 +31994,7 @@
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E687" t="n">
@@ -32015,7 +32015,7 @@
       </c>
       <c r="I687" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J687" t="inlineStr">
@@ -32030,7 +32030,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Joï¿½o Gabriel Campos</t>
+          <t>João Gabriel Campos</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -32061,7 +32061,7 @@
       </c>
       <c r="I688" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J688" t="inlineStr">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>Maria Cecï¿½lia Mendes</t>
+          <t>Maria Cecília Mendes</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -32127,7 +32127,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
@@ -32173,12 +32173,12 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E691" t="n">
@@ -32199,7 +32199,7 @@
       </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J691" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Joï¿½o Miguel Nogueira</t>
+          <t>João Miguel Nogueira</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -32224,7 +32224,7 @@
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E692" t="n">
@@ -32291,7 +32291,7 @@
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
@@ -32536,17 +32536,17 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Natï¿½lia Aragï¿½o</t>
+          <t>Natália Aragão</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E699" t="n">
@@ -32567,7 +32567,7 @@
       </c>
       <c r="I699" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J699" t="inlineStr">
@@ -32633,7 +32633,7 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
@@ -32659,7 +32659,7 @@
       </c>
       <c r="I701" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J701" t="inlineStr">
@@ -32679,7 +32679,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="I702" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J702" t="inlineStr">
@@ -32771,7 +32771,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -32863,7 +32863,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
@@ -32909,7 +32909,7 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -33052,7 +33052,7 @@
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E710" t="n">
@@ -33088,12 +33088,12 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>Natï¿½lia da Conceiï¿½ï¿½o</t>
+          <t>Natália da Conceição</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
@@ -33139,7 +33139,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -33165,7 +33165,7 @@
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J712" t="inlineStr">
@@ -33185,7 +33185,7 @@
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -33236,7 +33236,7 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E714" t="n">
@@ -33318,7 +33318,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Antï¿½nio Souza</t>
+          <t>Antônio Souza</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -33364,7 +33364,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Sra. Rafaela Araï¿½jo</t>
+          <t>Sra. Rafaela Araújo</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -33395,7 +33395,7 @@
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
@@ -33410,7 +33410,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Heloï¿½sa Nunes</t>
+          <t>Heloísa Nunes</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -33461,7 +33461,7 @@
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -33507,7 +33507,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -33533,7 +33533,7 @@
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
@@ -33548,7 +33548,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Joï¿½o Lucas Rezende</t>
+          <t>João Lucas Rezende</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -33579,7 +33579,7 @@
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
@@ -33594,7 +33594,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Cauï¿½ Pires</t>
+          <t>Cauã Pires</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -33625,7 +33625,7 @@
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
@@ -33691,7 +33691,7 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
@@ -33732,7 +33732,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Srta. Vitï¿½ria Freitas</t>
+          <t>Srta. Vitória Freitas</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -33875,7 +33875,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -33901,7 +33901,7 @@
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J728" t="inlineStr">
@@ -33921,7 +33921,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
@@ -33967,7 +33967,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -34018,7 +34018,7 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E731" t="n">
@@ -34039,7 +34039,7 @@
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J731" t="inlineStr">
@@ -34059,7 +34059,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -34085,7 +34085,7 @@
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
@@ -34100,7 +34100,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Heloï¿½sa Pires</t>
+          <t>Heloísa Pires</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -34269,7 +34269,7 @@
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
@@ -34289,7 +34289,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -34361,7 +34361,7 @@
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J738" t="inlineStr">
@@ -34381,7 +34381,7 @@
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
@@ -34427,7 +34427,7 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
@@ -34453,7 +34453,7 @@
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J740" t="inlineStr">
@@ -34519,7 +34519,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
@@ -34565,7 +34565,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
@@ -34606,7 +34606,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>Sr. Diogo da Conceiï¿½ï¿½o</t>
+          <t>Sr. Diogo da Conceição</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -34616,7 +34616,7 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E744" t="n">
@@ -34754,7 +34754,7 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E747" t="n">
@@ -34795,7 +34795,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
@@ -34821,7 +34821,7 @@
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
@@ -34836,12 +34836,12 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Ana Lï¿½via Azevedo</t>
+          <t>Ana Lívia Azevedo</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
@@ -34882,7 +34882,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Lï¿½via Rodrigues</t>
+          <t>Lívia Rodrigues</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
@@ -34892,7 +34892,7 @@
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E750" t="n">
@@ -34928,12 +34928,12 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Dra. Ana Vitï¿½ria Araï¿½jo</t>
+          <t>Dra. Ana Vitória Araújo</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
@@ -34974,12 +34974,12 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Lavï¿½nia Sales</t>
+          <t>Lavínia Sales</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
@@ -35005,7 +35005,7 @@
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J752" t="inlineStr">
@@ -35020,17 +35020,17 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Joï¿½o da Mata</t>
+          <t>João da Mata</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E753" t="n">
@@ -35071,7 +35071,7 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
@@ -35117,7 +35117,7 @@
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
@@ -35189,7 +35189,7 @@
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
@@ -35214,7 +35214,7 @@
       </c>
       <c r="D757" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E757" t="n">
@@ -35281,7 +35281,7 @@
       </c>
       <c r="I758" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J758" t="inlineStr">
@@ -35327,7 +35327,7 @@
       </c>
       <c r="I759" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J759" t="inlineStr">
@@ -35342,7 +35342,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>Antï¿½nio Cardoso</t>
+          <t>Antônio Cardoso</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -35388,7 +35388,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>Sra. Maria Cecï¿½lia Araï¿½jo</t>
+          <t>Sra. Maria Cecília Araújo</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -35490,7 +35490,7 @@
       </c>
       <c r="D763" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E763" t="n">
@@ -35511,7 +35511,7 @@
       </c>
       <c r="I763" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J763" t="inlineStr">
@@ -35531,7 +35531,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D764" t="inlineStr">
@@ -35577,7 +35577,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D765" t="inlineStr">
@@ -35618,12 +35618,12 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Jï¿½lia da Rocha</t>
+          <t>Júlia da Rocha</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D766" t="inlineStr">
@@ -35741,7 +35741,7 @@
       </c>
       <c r="I768" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J768" t="inlineStr">
@@ -35848,7 +35848,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>Joï¿½o Pedro Monteiro</t>
+          <t>João Pedro Monteiro</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -35950,7 +35950,7 @@
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E773" t="n">
@@ -36017,7 +36017,7 @@
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J774" t="inlineStr">
@@ -36078,7 +36078,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>Sra. Bï¿½rbara da Conceiï¿½ï¿½o</t>
+          <t>Sra. Bárbara da Conceição</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -36088,7 +36088,7 @@
       </c>
       <c r="D776" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E776" t="n">
@@ -36129,12 +36129,12 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E777" t="n">
@@ -36247,7 +36247,7 @@
       </c>
       <c r="I779" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J779" t="inlineStr">
@@ -36267,12 +36267,12 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E780" t="n">
@@ -36405,7 +36405,7 @@
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
@@ -36451,7 +36451,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -36477,7 +36477,7 @@
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
@@ -36492,7 +36492,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>Eduarda Fogaï¿½a</t>
+          <t>Eduarda Fogaça</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -36502,7 +36502,7 @@
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E785" t="n">
@@ -36569,7 +36569,7 @@
       </c>
       <c r="I786" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J786" t="inlineStr">
@@ -36635,7 +36635,7 @@
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
@@ -36661,7 +36661,7 @@
       </c>
       <c r="I788" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J788" t="inlineStr">
@@ -36727,7 +36727,7 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
@@ -36819,7 +36819,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
@@ -36865,7 +36865,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
@@ -36891,7 +36891,7 @@
       </c>
       <c r="I793" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J793" t="inlineStr">
@@ -36906,12 +36906,12 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>Joï¿½o Felipe Almeida</t>
+          <t>João Felipe Almeida</t>
         </is>
       </c>
       <c r="C794" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D794" t="inlineStr">
@@ -36962,7 +36962,7 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E795" t="n">
@@ -36983,7 +36983,7 @@
       </c>
       <c r="I795" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J795" t="inlineStr">
@@ -37003,12 +37003,12 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E796" t="n">
@@ -37029,7 +37029,7 @@
       </c>
       <c r="I796" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J796" t="inlineStr">
@@ -37095,7 +37095,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D798" t="inlineStr">
@@ -37121,7 +37121,7 @@
       </c>
       <c r="I798" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J798" t="inlineStr">
@@ -37136,7 +37136,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>Maitï¿½ da Mata</t>
+          <t>Maitê da Mata</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -37167,7 +37167,7 @@
       </c>
       <c r="I799" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J799" t="inlineStr">
@@ -37187,12 +37187,12 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D800" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E800" t="n">
@@ -37325,7 +37325,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D803" t="inlineStr">
@@ -37371,7 +37371,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D804" t="inlineStr">
@@ -37458,7 +37458,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>Maria Julia Gonï¿½alves</t>
+          <t>Maria Julia Gonçalves</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -37550,12 +37550,12 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>Natï¿½lia Lopes</t>
+          <t>Natália Lopes</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
@@ -37744,7 +37744,7 @@
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E812" t="n">
@@ -37780,12 +37780,12 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>Laï¿½s Silva</t>
+          <t>Laís Silva</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
@@ -37811,7 +37811,7 @@
       </c>
       <c r="I813" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J813" t="inlineStr">
@@ -37857,7 +37857,7 @@
       </c>
       <c r="I814" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J814" t="inlineStr">
@@ -37877,7 +37877,7 @@
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
@@ -37923,7 +37923,7 @@
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
@@ -38015,7 +38015,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
@@ -38061,7 +38061,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
@@ -38087,7 +38087,7 @@
       </c>
       <c r="I819" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J819" t="inlineStr">
@@ -38107,7 +38107,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -38148,7 +38148,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Maria Vitï¿½ria Oliveira</t>
+          <t>Maria Vitória Oliveira</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -38158,7 +38158,7 @@
       </c>
       <c r="D821" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E821" t="n">
@@ -38179,7 +38179,7 @@
       </c>
       <c r="I821" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J821" t="inlineStr">
@@ -38194,7 +38194,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>Joï¿½o Vitor das Neves</t>
+          <t>João Vitor das Neves</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -38204,7 +38204,7 @@
       </c>
       <c r="D822" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E822" t="n">
@@ -38225,7 +38225,7 @@
       </c>
       <c r="I822" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J822" t="inlineStr">
@@ -38271,7 +38271,7 @@
       </c>
       <c r="I823" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J823" t="inlineStr">
@@ -38286,12 +38286,12 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Maria Vitï¿½ria da Rocha</t>
+          <t>Maria Vitória da Rocha</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D824" t="inlineStr">
@@ -38332,7 +38332,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Eduarda Araï¿½jo</t>
+          <t>Eduarda Araújo</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -38363,7 +38363,7 @@
       </c>
       <c r="I825" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J825" t="inlineStr">
@@ -38429,12 +38429,12 @@
       </c>
       <c r="C827" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E827" t="n">
@@ -38475,7 +38475,7 @@
       </c>
       <c r="C828" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D828" t="inlineStr">
@@ -38593,7 +38593,7 @@
       </c>
       <c r="I830" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J830" t="inlineStr">
@@ -38659,12 +38659,12 @@
       </c>
       <c r="C832" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E832" t="n">
@@ -38710,7 +38710,7 @@
       </c>
       <c r="D833" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E833" t="n">
@@ -38777,7 +38777,7 @@
       </c>
       <c r="I834" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J834" t="inlineStr">
@@ -38797,7 +38797,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
@@ -38823,7 +38823,7 @@
       </c>
       <c r="I835" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J835" t="inlineStr">
@@ -38894,7 +38894,7 @@
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E837" t="n">
@@ -38940,7 +38940,7 @@
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E838" t="n">
@@ -38961,7 +38961,7 @@
       </c>
       <c r="I838" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J838" t="inlineStr">
@@ -39022,7 +39022,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>Joï¿½o Vitor da Conceiï¿½ï¿½o</t>
+          <t>João Vitor da Conceição</t>
         </is>
       </c>
       <c r="C840" t="inlineStr">
@@ -39078,7 +39078,7 @@
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E841" t="n">
@@ -39099,7 +39099,7 @@
       </c>
       <c r="I841" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J841" t="inlineStr">
@@ -39262,7 +39262,7 @@
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E845" t="n">
@@ -39298,17 +39298,17 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Andrï¿½ Sales</t>
+          <t>André Sales</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E846" t="n">
@@ -39395,12 +39395,12 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E848" t="n">
@@ -39513,7 +39513,7 @@
       </c>
       <c r="I850" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J850" t="inlineStr">
@@ -39533,7 +39533,7 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D851" t="inlineStr">
@@ -39579,7 +39579,7 @@
       </c>
       <c r="C852" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D852" t="inlineStr">
@@ -39671,7 +39671,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
@@ -39697,7 +39697,7 @@
       </c>
       <c r="I854" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J854" t="inlineStr">
@@ -39712,7 +39712,7 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>Maitï¿½ Novaes</t>
+          <t>Maitê Novaes</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -39768,7 +39768,7 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E856" t="n">
@@ -39789,7 +39789,7 @@
       </c>
       <c r="I856" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J856" t="inlineStr">
@@ -39804,12 +39804,12 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Juliana Fogaï¿½a</t>
+          <t>Juliana Fogaça</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D857" t="inlineStr">
@@ -39835,7 +39835,7 @@
       </c>
       <c r="I857" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J857" t="inlineStr">
@@ -39850,7 +39850,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Joï¿½o Lucas da Conceiï¿½ï¿½o</t>
+          <t>João Lucas da Conceição</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -39901,7 +39901,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
@@ -39947,7 +39947,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
@@ -40039,7 +40039,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
@@ -40126,7 +40126,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>Joï¿½o Vitor Nogueira</t>
+          <t>João Vitor Nogueira</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -40172,7 +40172,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>Lavï¿½nia Dias</t>
+          <t>Lavínia Dias</t>
         </is>
       </c>
       <c r="C865" t="inlineStr">
@@ -40269,7 +40269,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
@@ -40310,7 +40310,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>Srta. Jï¿½lia Caldeira</t>
+          <t>Srta. Júlia Caldeira</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -40361,12 +40361,12 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E869" t="n">
@@ -40412,7 +40412,7 @@
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E870" t="n">
@@ -40448,7 +40448,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Joï¿½o das Neves</t>
+          <t>João das Neves</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -40591,12 +40591,12 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E874" t="n">
@@ -40617,7 +40617,7 @@
       </c>
       <c r="I874" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J874" t="inlineStr">
@@ -40683,7 +40683,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
@@ -40770,17 +40770,17 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>Joï¿½o Felipe das Neves</t>
+          <t>João Felipe das Neves</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E878" t="n">
@@ -40801,7 +40801,7 @@
       </c>
       <c r="I878" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J878" t="inlineStr">
@@ -40816,7 +40816,7 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>Benï¿½cio Barbosa</t>
+          <t>Benício Barbosa</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -40847,7 +40847,7 @@
       </c>
       <c r="I879" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J879" t="inlineStr">
@@ -40862,7 +40862,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>Joï¿½o Miguel da Costa</t>
+          <t>João Miguel da Costa</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
@@ -41092,7 +41092,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Dr. Antï¿½nio Pinto</t>
+          <t>Dr. Antônio Pinto</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -41189,7 +41189,7 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D887" t="inlineStr">
@@ -41230,7 +41230,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>Sra. Caroline Araï¿½jo</t>
+          <t>Sra. Caroline Araújo</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -41276,7 +41276,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>Luana da Conceiï¿½ï¿½o</t>
+          <t>Luana da Conceição</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -41286,7 +41286,7 @@
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E889" t="n">
@@ -41322,12 +41322,12 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>Lï¿½via Pires</t>
+          <t>Lívia Pires</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D890" t="inlineStr">
@@ -41368,12 +41368,12 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>Emilly da Conceiï¿½ï¿½o</t>
+          <t>Emilly da Conceição</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
@@ -41506,12 +41506,12 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>Ana Vitï¿½ria Alves</t>
+          <t>Ana Vitória Alves</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
@@ -41603,7 +41603,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -41629,7 +41629,7 @@
       </c>
       <c r="I896" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J896" t="inlineStr">
@@ -41767,7 +41767,7 @@
       </c>
       <c r="I899" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J899" t="inlineStr">
@@ -41905,7 +41905,7 @@
       </c>
       <c r="I902" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J902" t="inlineStr">
@@ -41925,7 +41925,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -41971,7 +41971,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
@@ -42022,7 +42022,7 @@
       </c>
       <c r="D905" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E905" t="n">
@@ -42063,12 +42063,12 @@
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D906" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E906" t="n">
@@ -42339,7 +42339,7 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D912" t="inlineStr">
@@ -42380,7 +42380,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>Dra. Maria Vitï¿½ria Peixoto</t>
+          <t>Dra. Maria Vitória Peixoto</t>
         </is>
       </c>
       <c r="C913" t="inlineStr">
@@ -42426,12 +42426,12 @@
       </c>
       <c r="B914" t="inlineStr">
         <is>
-          <t>Dra. Jï¿½lia Pinto</t>
+          <t>Dra. Júlia Pinto</t>
         </is>
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D914" t="inlineStr">
@@ -42569,7 +42569,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D917" t="inlineStr">
@@ -42661,7 +42661,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D919" t="inlineStr">
@@ -42707,7 +42707,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D920" t="inlineStr">
@@ -42733,7 +42733,7 @@
       </c>
       <c r="I920" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J920" t="inlineStr">
@@ -42748,7 +42748,7 @@
       </c>
       <c r="B921" t="inlineStr">
         <is>
-          <t>Dra. Laura da Conceiï¿½ï¿½o</t>
+          <t>Dra. Laura da Conceição</t>
         </is>
       </c>
       <c r="C921" t="inlineStr">
@@ -42779,7 +42779,7 @@
       </c>
       <c r="I921" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J921" t="inlineStr">
@@ -42794,7 +42794,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>Vitï¿½ria Farias</t>
+          <t>Vitória Farias</t>
         </is>
       </c>
       <c r="C922" t="inlineStr">
@@ -42804,7 +42804,7 @@
       </c>
       <c r="D922" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E922" t="n">
@@ -42825,7 +42825,7 @@
       </c>
       <c r="I922" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J922" t="inlineStr">
@@ -42917,7 +42917,7 @@
       </c>
       <c r="I924" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J924" t="inlineStr">
@@ -42978,7 +42978,7 @@
       </c>
       <c r="B926" t="inlineStr">
         <is>
-          <t>Luiz Otï¿½vio Azevedo</t>
+          <t>Luiz Otávio Azevedo</t>
         </is>
       </c>
       <c r="C926" t="inlineStr">
@@ -43009,7 +43009,7 @@
       </c>
       <c r="I926" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J926" t="inlineStr">
@@ -43024,7 +43024,7 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>Davi Lucas Gonï¿½alves</t>
+          <t>Davi Lucas Gonçalves</t>
         </is>
       </c>
       <c r="C927" t="inlineStr">
@@ -43070,12 +43070,12 @@
       </c>
       <c r="B928" t="inlineStr">
         <is>
-          <t>Dr. Antï¿½nio Ramos</t>
+          <t>Dr. Antônio Ramos</t>
         </is>
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D928" t="inlineStr">
@@ -43213,12 +43213,12 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D931" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E931" t="n">
@@ -43346,7 +43346,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>Benï¿½cio da Cunha</t>
+          <t>Benício da Cunha</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
@@ -43356,7 +43356,7 @@
       </c>
       <c r="D934" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E934" t="n">
@@ -43402,7 +43402,7 @@
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E935" t="n">
@@ -43489,7 +43489,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
@@ -43576,7 +43576,7 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>Laï¿½s Gonï¿½alves</t>
+          <t>Laís Gonçalves</t>
         </is>
       </c>
       <c r="C939" t="inlineStr">
@@ -43607,7 +43607,7 @@
       </c>
       <c r="I939" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J939" t="inlineStr">
@@ -43627,7 +43627,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
@@ -43678,7 +43678,7 @@
       </c>
       <c r="D941" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E941" t="n">
@@ -43765,7 +43765,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
@@ -43791,7 +43791,7 @@
       </c>
       <c r="I943" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J943" t="inlineStr">
@@ -43806,7 +43806,7 @@
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>Alï¿½cia das Neves</t>
+          <t>Alícia das Neves</t>
         </is>
       </c>
       <c r="C944" t="inlineStr">
@@ -43852,7 +43852,7 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>Isaac Aragï¿½o</t>
+          <t>Isaac Aragão</t>
         </is>
       </c>
       <c r="C945" t="inlineStr">
@@ -43862,7 +43862,7 @@
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E945" t="n">
@@ -43883,7 +43883,7 @@
       </c>
       <c r="I945" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J945" t="inlineStr">
@@ -43975,7 +43975,7 @@
       </c>
       <c r="I947" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J947" t="inlineStr">
@@ -43990,17 +43990,17 @@
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>Enzo Gabriel Aragï¿½o</t>
+          <t>Enzo Gabriel Aragão</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E948" t="n">
@@ -44133,7 +44133,7 @@
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
@@ -44501,12 +44501,12 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D959" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E959" t="n">
@@ -44588,7 +44588,7 @@
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>Joï¿½o Gabriel da Mata</t>
+          <t>João Gabriel da Mata</t>
         </is>
       </c>
       <c r="C961" t="inlineStr">
@@ -44639,7 +44639,7 @@
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D962" t="inlineStr">
@@ -44680,12 +44680,12 @@
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>Joï¿½o Felipe Fernandes</t>
+          <t>João Felipe Fernandes</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D963" t="inlineStr">
@@ -44731,7 +44731,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D964" t="inlineStr">
@@ -44782,7 +44782,7 @@
       </c>
       <c r="D965" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E965" t="n">
@@ -44874,7 +44874,7 @@
       </c>
       <c r="D967" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E967" t="n">
@@ -44895,7 +44895,7 @@
       </c>
       <c r="I967" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J967" t="inlineStr">
@@ -44910,7 +44910,7 @@
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>Lavï¿½nia Pires</t>
+          <t>Lavínia Pires</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
@@ -44966,7 +44966,7 @@
       </c>
       <c r="D969" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E969" t="n">
@@ -45012,7 +45012,7 @@
       </c>
       <c r="D970" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E970" t="n">
@@ -45053,7 +45053,7 @@
       </c>
       <c r="C971" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D971" t="inlineStr">
@@ -45196,7 +45196,7 @@
       </c>
       <c r="D974" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E974" t="n">
@@ -45232,12 +45232,12 @@
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>Sr. Joï¿½o Lucas Almeida</t>
+          <t>Sr. João Lucas Almeida</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D975" t="inlineStr">
@@ -45288,7 +45288,7 @@
       </c>
       <c r="D976" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E976" t="n">
@@ -45324,7 +45324,7 @@
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>Ana Vitï¿½ria Freitas</t>
+          <t>Ana Vitória Freitas</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
@@ -45334,7 +45334,7 @@
       </c>
       <c r="D977" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E977" t="n">
@@ -45416,7 +45416,7 @@
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Fernando Gonï¿½alves</t>
+          <t>Fernando Gonçalves</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
@@ -45513,7 +45513,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D981" t="inlineStr">
@@ -45559,7 +45559,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D982" t="inlineStr">
@@ -45600,12 +45600,12 @@
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>Joï¿½o Moraes</t>
+          <t>João Moraes</t>
         </is>
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D983" t="inlineStr">
@@ -45631,7 +45631,7 @@
       </c>
       <c r="I983" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J983" t="inlineStr">
@@ -45677,7 +45677,7 @@
       </c>
       <c r="I984" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J984" t="inlineStr">
@@ -45748,7 +45748,7 @@
       </c>
       <c r="D986" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E986" t="n">
@@ -45830,7 +45830,7 @@
       </c>
       <c r="B988" t="inlineStr">
         <is>
-          <t>Maitï¿½ Cardoso</t>
+          <t>Maitê Cardoso</t>
         </is>
       </c>
       <c r="C988" t="inlineStr">
@@ -45861,7 +45861,7 @@
       </c>
       <c r="I988" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J988" t="inlineStr">
@@ -45973,7 +45973,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D991" t="inlineStr">
@@ -46019,7 +46019,7 @@
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D992" t="inlineStr">
@@ -46045,7 +46045,7 @@
       </c>
       <c r="I992" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J992" t="inlineStr">
@@ -46065,7 +46065,7 @@
       </c>
       <c r="C993" t="inlineStr">
         <is>
-          <t>Logï¿½stica</t>
+          <t>Logística</t>
         </is>
       </c>
       <c r="D993" t="inlineStr">
@@ -46091,7 +46091,7 @@
       </c>
       <c r="I993" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J993" t="inlineStr">
@@ -46152,7 +46152,7 @@
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>Ana Lï¿½via Cardoso</t>
+          <t>Ana Lívia Cardoso</t>
         </is>
       </c>
       <c r="C995" t="inlineStr">
@@ -46229,7 +46229,7 @@
       </c>
       <c r="I996" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J996" t="inlineStr">
@@ -46244,7 +46244,7 @@
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>Matheus Aragï¿½o</t>
+          <t>Matheus Aragão</t>
         </is>
       </c>
       <c r="C997" t="inlineStr">
@@ -46275,7 +46275,7 @@
       </c>
       <c r="I997" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J997" t="inlineStr">
@@ -46321,7 +46321,7 @@
       </c>
       <c r="I998" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J998" t="inlineStr">
@@ -46387,7 +46387,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D1000" t="inlineStr">
@@ -46433,12 +46433,12 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>Produï¿½ï¿½o</t>
+          <t>Produção</t>
         </is>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
-          <t>Tï¿½cnico</t>
+          <t>Técnico</t>
         </is>
       </c>
       <c r="E1001" t="n">
@@ -46459,7 +46459,7 @@
       </c>
       <c r="I1001" t="inlineStr">
         <is>
-          <t>Viï¿½vo</t>
+          <t>Viúvo</t>
         </is>
       </c>
       <c r="J1001" t="inlineStr">
